--- a/NURBS IDX11 PYTHON ANALYSIS/8_4_2026_Redo_front/15gps/4mps_15gps_analysis.xlsx
+++ b/NURBS IDX11 PYTHON ANALYSIS/8_4_2026_Redo_front/15gps/4mps_15gps_analysis.xlsx
@@ -691,7 +691,7 @@
         <v>0</v>
       </c>
       <c r="W3">
-        <v>481.6215375352495</v>
+        <v>481.7457790667899</v>
       </c>
       <c r="X3">
         <v>0.245508024</v>
@@ -866,10 +866,10 @@
         <v>480.6525346810432</v>
       </c>
       <c r="V5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W5">
-        <v>23.39675980107645</v>
+        <v>23.39793098181051</v>
       </c>
       <c r="X5">
         <v>0.24550485</v>
@@ -955,7 +955,7 @@
         <v>478.7354158713429</v>
       </c>
       <c r="V6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X6">
         <v>0.245485482</v>
@@ -1041,7 +1041,7 @@
         <v>480.2760723721452</v>
       </c>
       <c r="V7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X7">
         <v>0.24547151</v>
@@ -1127,7 +1127,7 @@
         <v>478.6221861347958</v>
       </c>
       <c r="V8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X8">
         <v>0.245458492</v>
